--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260526_212639.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260526_212639.xlsx
@@ -6332,7 +6332,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260526_212639.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260526_212639.xlsx
@@ -6332,7 +6332,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
